--- a/output/pdf_financials_xlsx/QEC.xlsx
+++ b/output/pdf_financials_xlsx/QEC.xlsx
@@ -2171,7 +2171,7 @@
         <v>-0.073534</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.000169</v>
+        <v>-0.000169</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.024821</v>
@@ -6927,7 +6927,7 @@
         <v>-0.073534</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.000169</v>
+        <v>-0.000169</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-0.024821</v>
@@ -8015,49 +8015,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-26.141328</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-6.449488</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.025363</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.031946</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06071</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.018283</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.010917</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.00445</v>
+        <v>-0.012876</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.017981</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014245</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004163</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.008812</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005498</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.016594</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.016008</v>
       </c>
     </row>
     <row r="119">
@@ -39828,7 +39828,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E311" s="5" t="n">
         <v>0.9700029999999999</v>
       </c>
@@ -42189,7 +42193,7 @@
         <v>-0.073534</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.000169</v>
+        <v>-0.000169</v>
       </c>
       <c r="N334" s="5" t="n">
         <v>-0.024821</v>
@@ -43737,7 +43741,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -45876,7 +45884,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -53688,7 +53700,11 @@
           <t>Exploration and evaluation expenditures 11</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -56403,7 +56419,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QEC.xlsx
+++ b/output/pdf_financials_xlsx/QEC.xlsx
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-1.501223</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.47806</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1.509498</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.735702</v>
+        <v>-5.234479</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-17.882614</v>
+        <v>-17.404554</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-18.302527</v>
+        <v>-16.793029</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2637,13 +2637,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>10.498851</v>
+        <v>12.000074</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.009459</v>
+        <v>-1.531399</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-12.549381</v>
+        <v>-11.039883</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>42.28894510040434</v>
+        <v>48.33581032693859</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-16.81197180718287</v>
+        <v>-12.81232252738077</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-120.2780486430338</v>
+        <v>-105.8104447133609</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -8390,22 +8390,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000108</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-5.8e-05</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-6.499999999999999e-05</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000243</v>
       </c>
     </row>
     <row r="125">
@@ -8448,22 +8448,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000108</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-5.3e-05</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-5.8e-05</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-6.499999999999999e-05</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000243</v>
       </c>
     </row>
     <row r="126">
@@ -44430,7 +44430,11 @@
           <t>Principal portion of lease payments 16</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -46052,7 +46056,11 @@
           <t>Principal portion of lease payments 19</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -48548,7 +48556,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -63861,7 +63873,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E554" s="5" t="n">
@@ -65760,7 +65772,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E573" s="5" t="n">

--- a/output/pdf_financials_xlsx/QEC.xlsx
+++ b/output/pdf_financials_xlsx/QEC.xlsx
@@ -2182,15 +2182,11 @@
       <c r="M23" s="3" t="n">
         <v>0.065704</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>-0.004301</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.014067</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-0.023708</v>
@@ -5195,22 +5191,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.000101</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>5.9e-05</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>5.8e-05</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.0009879999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5253,22 +5249,22 @@
         <v>0.013842</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.016377</v>
+        <v>0.016478</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.00342</v>
+        <v>0.003472</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.3e-05</v>
+        <v>9.2e-05</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.6e-05</v>
+        <v>9.399999999999999e-05</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>4.9e-05</v>
+        <v>0.000105</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.0009879999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5485,19 +5481,19 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.000101</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>5.2e-05</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.000543</v>
+        <v>0.000484</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.000242</v>
+        <v>0.000184</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.000806</v>
+        <v>0.00075</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0.007327</v>
@@ -5789,24 +5785,22 @@
         <v>0.07390638097933162</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.06095899589065571</v>
+        <v>0.06133494133762134</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.02295902954464591</v>
+        <v>0.02330811420438907</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.0001986420109794857</v>
+        <v>0.0005537898487912935</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.0002505794650128422</v>
+        <v>0.0006542908253113101</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.0003534613969660028</v>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0007574172792128631</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.01288824534627376</v>
       </c>
     </row>
     <row r="81">
@@ -6938,15 +6932,11 @@
       <c r="M99" s="3" t="n">
         <v>0.065704</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>-0.004301</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0.014067</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-0.023708</v>
@@ -7777,7 +7767,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.295942</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -7786,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.494506</v>
+        <v>-2.326944</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>-0.043171</v>
@@ -7841,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.52586</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7850,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.00049</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -8192,10 +8182,10 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-3.312404</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00052</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -11031,7 +11021,11 @@
           <t>Lease liabilities 16</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -14813,7 +14807,11 @@
           <t>Lease liabilities 19</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -16938,7 +16936,11 @@
           <t>Lease liabilities 19 $</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -42846,7 +42848,11 @@
           <t>Deferred tax recovery 12</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -46252,7 +46258,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -47026,7 +47036,11 @@
           <t>Deferred tax expense (recovery) 10</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -48188,7 +48202,11 @@
           <t>Deferred tax expense 10</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -51817,7 +51835,11 @@
           <t>Deferred tax recovery 10,11</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -52318,7 +52340,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -54530,7 +54556,11 @@
           <t>Shares repurchased 16</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -55730,7 +55760,11 @@
           <t>Deferred taxes (recovery) 14</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -56835,7 +56869,11 @@
           <t>Purchase of marketable securities 6</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -57346,7 +57384,11 @@
           <t>Shares repurchased 17</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr">
         <is>
           <t>-</t>
@@ -58249,7 +58291,11 @@
           <t>Deferred taxes (recovery) 16</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -58954,7 +59000,11 @@
           <t>Purchase of marketable securities 6</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -60374,7 +60424,11 @@
           <t>Future income tax recovery (note 8 &amp; restated note 14)</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -62178,7 +62232,11 @@
           <t>Future income taxes (recovery) (note 9)</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E537" s="5" t="n">
         <v>2.409352</v>
       </c>
@@ -62780,7 +62838,11 @@
           <t>Purchase of marketable securities (note 5)</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E543" s="5" t="n">
         <v>-0.295942</v>
       </c>
